--- a/artfynd/A 25051-2023 artfynd.xlsx
+++ b/artfynd/A 25051-2023 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>119833907</v>
+        <v>119833795</v>
       </c>
       <c r="B2" t="n">
-        <v>82305</v>
+        <v>78526</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,37 +691,37 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>1312</v>
+        <v>6425</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Lillrået, Lillrået, Ång</t>
+          <t>Lillrået, Ång</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>563078</v>
+        <v>563058</v>
       </c>
       <c r="R2" t="n">
-        <v>7062343</v>
+        <v>7062361</v>
       </c>
       <c r="S2" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -748,19 +748,9 @@
           <t>2024-09-18</t>
         </is>
       </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>13:59</t>
-        </is>
-      </c>
       <c r="AA2" t="inlineStr">
         <is>
           <t>2024-09-18</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>13:59</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -775,22 +765,22 @@
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Michaela Ehmann</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Michaela Ehmann</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>119833795</v>
+        <v>119834324</v>
       </c>
       <c r="B3" t="n">
-        <v>78526</v>
+        <v>79607</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -803,21 +793,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -827,7 +817,7 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>563058</v>
+        <v>563099</v>
       </c>
       <c r="R3" t="n">
         <v>7062361</v>
@@ -889,10 +879,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>119834324</v>
+        <v>119834486</v>
       </c>
       <c r="B4" t="n">
-        <v>79607</v>
+        <v>57421</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -901,41 +891,55 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6458</v>
+        <v>103031</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Lavskrika</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Perisoreus infaustus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="L4" t="inlineStr">
+        <is>
+          <t>i par</t>
+        </is>
+      </c>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>stationär</t>
+        </is>
+      </c>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Lillrået, Ång</t>
+          <t>Lillrået, Lillrået, Ång</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>563099</v>
+        <v>563091</v>
       </c>
       <c r="R4" t="n">
-        <v>7062361</v>
+        <v>7062368</v>
       </c>
       <c r="S4" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -962,9 +966,19 @@
           <t>2024-09-18</t>
         </is>
       </c>
+      <c r="Z4" t="inlineStr">
+        <is>
+          <t>14:34</t>
+        </is>
+      </c>
       <c r="AA4" t="inlineStr">
         <is>
           <t>2024-09-18</t>
+        </is>
+      </c>
+      <c r="AB4" t="inlineStr">
+        <is>
+          <t>14:34</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -979,22 +993,22 @@
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>Michaela Ehmann</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Michaela Ehmann</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>119834486</v>
+        <v>119833884</v>
       </c>
       <c r="B5" t="n">
-        <v>57421</v>
+        <v>79607</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1003,55 +1017,41 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>103031</v>
+        <v>6458</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Lavskrika</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Perisoreus infaustus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="L5" t="inlineStr">
-        <is>
-          <t>i par</t>
-        </is>
-      </c>
-      <c r="M5" t="inlineStr">
-        <is>
-          <t>stationär</t>
-        </is>
-      </c>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
           <t>Lillrået, Lillrået, Ång</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>563091</v>
+        <v>563090</v>
       </c>
       <c r="R5" t="n">
-        <v>7062368</v>
+        <v>7062388</v>
       </c>
       <c r="S5" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1078,19 +1078,9 @@
           <t>2024-09-18</t>
         </is>
       </c>
-      <c r="Z5" t="inlineStr">
-        <is>
-          <t>14:34</t>
-        </is>
-      </c>
       <c r="AA5" t="inlineStr">
         <is>
           <t>2024-09-18</t>
-        </is>
-      </c>
-      <c r="AB5" t="inlineStr">
-        <is>
-          <t>14:34</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1105,22 +1095,22 @@
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>119833884</v>
+        <v>119833907</v>
       </c>
       <c r="B6" t="n">
-        <v>79607</v>
+        <v>82305</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1133,21 +1123,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6458</v>
+        <v>1312</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1157,13 +1147,13 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>563090</v>
+        <v>563078</v>
       </c>
       <c r="R6" t="n">
-        <v>7062388</v>
+        <v>7062343</v>
       </c>
       <c r="S6" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1190,9 +1180,19 @@
           <t>2024-09-18</t>
         </is>
       </c>
+      <c r="Z6" t="inlineStr">
+        <is>
+          <t>13:59</t>
+        </is>
+      </c>
       <c r="AA6" t="inlineStr">
         <is>
           <t>2024-09-18</t>
+        </is>
+      </c>
+      <c r="AB6" t="inlineStr">
+        <is>
+          <t>13:59</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1207,12 +1207,12 @@
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>

--- a/artfynd/A 25051-2023 artfynd.xlsx
+++ b/artfynd/A 25051-2023 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>119833795</v>
+        <v>119834486</v>
       </c>
       <c r="B2" t="n">
-        <v>78526</v>
+        <v>57421</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,41 +687,55 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6425</v>
+        <v>103031</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lavskrika</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Perisoreus infaustus</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="L2" t="inlineStr">
+        <is>
+          <t>i par</t>
+        </is>
+      </c>
+      <c r="M2" t="inlineStr">
+        <is>
+          <t>stationär</t>
+        </is>
+      </c>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Lillrået, Ång</t>
+          <t>Lillrået, Lillrået, Ång</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>563058</v>
+        <v>563091</v>
       </c>
       <c r="R2" t="n">
-        <v>7062361</v>
+        <v>7062368</v>
       </c>
       <c r="S2" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -748,9 +762,19 @@
           <t>2024-09-18</t>
         </is>
       </c>
+      <c r="Z2" t="inlineStr">
+        <is>
+          <t>14:34</t>
+        </is>
+      </c>
       <c r="AA2" t="inlineStr">
         <is>
           <t>2024-09-18</t>
+        </is>
+      </c>
+      <c r="AB2" t="inlineStr">
+        <is>
+          <t>14:34</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -765,12 +789,12 @@
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>Michaela Ehmann</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Michaela Ehmann</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
@@ -879,10 +903,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>119834486</v>
+        <v>119833907</v>
       </c>
       <c r="B4" t="n">
-        <v>57421</v>
+        <v>82305</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -891,52 +915,38 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>103031</v>
+        <v>1312</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Lavskrika</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Perisoreus infaustus</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="L4" t="inlineStr">
-        <is>
-          <t>i par</t>
-        </is>
-      </c>
-      <c r="M4" t="inlineStr">
-        <is>
-          <t>stationär</t>
-        </is>
-      </c>
+          <t>(Nyl.) Rehm</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
           <t>Lillrået, Lillrået, Ång</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>563091</v>
+        <v>563078</v>
       </c>
       <c r="R4" t="n">
-        <v>7062368</v>
+        <v>7062343</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -968,7 +978,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>14:34</t>
+          <t>13:59</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -978,7 +988,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>14:34</t>
+          <t>13:59</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1005,10 +1015,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>119833884</v>
+        <v>119833795</v>
       </c>
       <c r="B5" t="n">
-        <v>79607</v>
+        <v>78526</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1021,34 +1031,34 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Lillrået, Lillrået, Ång</t>
+          <t>Lillrået, Ång</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>563090</v>
+        <v>563058</v>
       </c>
       <c r="R5" t="n">
-        <v>7062388</v>
+        <v>7062361</v>
       </c>
       <c r="S5" t="n">
         <v>15</v>
@@ -1095,22 +1105,22 @@
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Michaela Ehmann</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Michaela Ehmann</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>119833907</v>
+        <v>119833884</v>
       </c>
       <c r="B6" t="n">
-        <v>82305</v>
+        <v>79607</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1123,21 +1133,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>1312</v>
+        <v>6458</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1147,13 +1157,13 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>563078</v>
+        <v>563090</v>
       </c>
       <c r="R6" t="n">
-        <v>7062343</v>
+        <v>7062388</v>
       </c>
       <c r="S6" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1180,19 +1190,9 @@
           <t>2024-09-18</t>
         </is>
       </c>
-      <c r="Z6" t="inlineStr">
-        <is>
-          <t>13:59</t>
-        </is>
-      </c>
       <c r="AA6" t="inlineStr">
         <is>
           <t>2024-09-18</t>
-        </is>
-      </c>
-      <c r="AB6" t="inlineStr">
-        <is>
-          <t>13:59</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1207,12 +1207,12 @@
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>

--- a/artfynd/A 25051-2023 artfynd.xlsx
+++ b/artfynd/A 25051-2023 artfynd.xlsx
@@ -903,10 +903,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>119833907</v>
+        <v>119833884</v>
       </c>
       <c r="B4" t="n">
-        <v>82305</v>
+        <v>79607</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -919,21 +919,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>1312</v>
+        <v>6458</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -943,13 +943,13 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>563078</v>
+        <v>563090</v>
       </c>
       <c r="R4" t="n">
-        <v>7062343</v>
+        <v>7062388</v>
       </c>
       <c r="S4" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -976,19 +976,9 @@
           <t>2024-09-18</t>
         </is>
       </c>
-      <c r="Z4" t="inlineStr">
-        <is>
-          <t>13:59</t>
-        </is>
-      </c>
       <c r="AA4" t="inlineStr">
         <is>
           <t>2024-09-18</t>
-        </is>
-      </c>
-      <c r="AB4" t="inlineStr">
-        <is>
-          <t>13:59</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1003,22 +993,22 @@
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>119833795</v>
+        <v>119833907</v>
       </c>
       <c r="B5" t="n">
-        <v>78526</v>
+        <v>82305</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1031,37 +1021,37 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6425</v>
+        <v>1312</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Lillrået, Ång</t>
+          <t>Lillrået, Lillrået, Ång</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>563058</v>
+        <v>563078</v>
       </c>
       <c r="R5" t="n">
-        <v>7062361</v>
+        <v>7062343</v>
       </c>
       <c r="S5" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1088,9 +1078,19 @@
           <t>2024-09-18</t>
         </is>
       </c>
+      <c r="Z5" t="inlineStr">
+        <is>
+          <t>13:59</t>
+        </is>
+      </c>
       <c r="AA5" t="inlineStr">
         <is>
           <t>2024-09-18</t>
+        </is>
+      </c>
+      <c r="AB5" t="inlineStr">
+        <is>
+          <t>13:59</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1105,22 +1105,22 @@
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>Michaela Ehmann</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Michaela Ehmann</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>119833884</v>
+        <v>119833795</v>
       </c>
       <c r="B6" t="n">
-        <v>79607</v>
+        <v>78526</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1133,34 +1133,34 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Lillrået, Lillrået, Ång</t>
+          <t>Lillrået, Ång</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>563090</v>
+        <v>563058</v>
       </c>
       <c r="R6" t="n">
-        <v>7062388</v>
+        <v>7062361</v>
       </c>
       <c r="S6" t="n">
         <v>15</v>
@@ -1207,12 +1207,12 @@
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Michaela Ehmann</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Michaela Ehmann</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>

--- a/artfynd/A 25051-2023 artfynd.xlsx
+++ b/artfynd/A 25051-2023 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>119834486</v>
+        <v>119833795</v>
       </c>
       <c r="B2" t="n">
-        <v>57421</v>
+        <v>78542</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,55 +687,41 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>103031</v>
+        <v>6425</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Lavskrika</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Perisoreus infaustus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="L2" t="inlineStr">
-        <is>
-          <t>i par</t>
-        </is>
-      </c>
-      <c r="M2" t="inlineStr">
-        <is>
-          <t>stationär</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Lillrået, Lillrået, Ång</t>
+          <t>Lillrået, Ång</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>563091</v>
+        <v>563058</v>
       </c>
       <c r="R2" t="n">
-        <v>7062368</v>
+        <v>7062361</v>
       </c>
       <c r="S2" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -762,19 +748,9 @@
           <t>2024-09-18</t>
         </is>
       </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>14:34</t>
-        </is>
-      </c>
       <c r="AA2" t="inlineStr">
         <is>
           <t>2024-09-18</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>14:34</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -789,12 +765,12 @@
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Michaela Ehmann</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Michaela Ehmann</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
@@ -804,7 +780,7 @@
         <v>119834324</v>
       </c>
       <c r="B3" t="n">
-        <v>79607</v>
+        <v>79623</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -906,7 +882,7 @@
         <v>119833884</v>
       </c>
       <c r="B4" t="n">
-        <v>79607</v>
+        <v>79623</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -1008,7 +984,7 @@
         <v>119833907</v>
       </c>
       <c r="B5" t="n">
-        <v>82305</v>
+        <v>82321</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1117,10 +1093,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>119833795</v>
+        <v>119834486</v>
       </c>
       <c r="B6" t="n">
-        <v>78526</v>
+        <v>57431</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1129,41 +1105,55 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6425</v>
+        <v>103031</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lavskrika</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Perisoreus infaustus</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="L6" t="inlineStr">
+        <is>
+          <t>i par</t>
+        </is>
+      </c>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>stationär</t>
+        </is>
+      </c>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Lillrået, Ång</t>
+          <t>Lillrået, Lillrået, Ång</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>563058</v>
+        <v>563091</v>
       </c>
       <c r="R6" t="n">
-        <v>7062361</v>
+        <v>7062368</v>
       </c>
       <c r="S6" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1190,9 +1180,19 @@
           <t>2024-09-18</t>
         </is>
       </c>
+      <c r="Z6" t="inlineStr">
+        <is>
+          <t>14:34</t>
+        </is>
+      </c>
       <c r="AA6" t="inlineStr">
         <is>
           <t>2024-09-18</t>
+        </is>
+      </c>
+      <c r="AB6" t="inlineStr">
+        <is>
+          <t>14:34</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1207,12 +1207,12 @@
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>Michaela Ehmann</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Michaela Ehmann</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>

--- a/artfynd/A 25051-2023 artfynd.xlsx
+++ b/artfynd/A 25051-2023 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>119833795</v>
+        <v>119834486</v>
       </c>
       <c r="B2" t="n">
-        <v>78542</v>
+        <v>57431</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,41 +687,55 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6425</v>
+        <v>103031</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lavskrika</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Perisoreus infaustus</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="L2" t="inlineStr">
+        <is>
+          <t>i par</t>
+        </is>
+      </c>
+      <c r="M2" t="inlineStr">
+        <is>
+          <t>stationär</t>
+        </is>
+      </c>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Lillrået, Ång</t>
+          <t>Lillrået, Lillrået, Ång</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>563058</v>
+        <v>563091</v>
       </c>
       <c r="R2" t="n">
-        <v>7062361</v>
+        <v>7062368</v>
       </c>
       <c r="S2" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -748,9 +762,19 @@
           <t>2024-09-18</t>
         </is>
       </c>
+      <c r="Z2" t="inlineStr">
+        <is>
+          <t>14:34</t>
+        </is>
+      </c>
       <c r="AA2" t="inlineStr">
         <is>
           <t>2024-09-18</t>
+        </is>
+      </c>
+      <c r="AB2" t="inlineStr">
+        <is>
+          <t>14:34</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -765,22 +789,22 @@
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>Michaela Ehmann</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Michaela Ehmann</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>119834324</v>
+        <v>119833795</v>
       </c>
       <c r="B3" t="n">
-        <v>79623</v>
+        <v>78542</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -793,21 +817,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -817,7 +841,7 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>563099</v>
+        <v>563058</v>
       </c>
       <c r="R3" t="n">
         <v>7062361</v>
@@ -981,10 +1005,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>119833907</v>
+        <v>119834324</v>
       </c>
       <c r="B5" t="n">
-        <v>82321</v>
+        <v>79623</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -997,37 +1021,37 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>1312</v>
+        <v>6458</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Lillrået, Lillrået, Ång</t>
+          <t>Lillrået, Ång</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>563078</v>
+        <v>563099</v>
       </c>
       <c r="R5" t="n">
-        <v>7062343</v>
+        <v>7062361</v>
       </c>
       <c r="S5" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1054,19 +1078,9 @@
           <t>2024-09-18</t>
         </is>
       </c>
-      <c r="Z5" t="inlineStr">
-        <is>
-          <t>13:59</t>
-        </is>
-      </c>
       <c r="AA5" t="inlineStr">
         <is>
           <t>2024-09-18</t>
-        </is>
-      </c>
-      <c r="AB5" t="inlineStr">
-        <is>
-          <t>13:59</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1081,22 +1095,22 @@
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Michaela Ehmann</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Michaela Ehmann</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>119834486</v>
+        <v>119833907</v>
       </c>
       <c r="B6" t="n">
-        <v>57431</v>
+        <v>82321</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1105,52 +1119,38 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>103031</v>
+        <v>1312</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Lavskrika</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Perisoreus infaustus</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="L6" t="inlineStr">
-        <is>
-          <t>i par</t>
-        </is>
-      </c>
-      <c r="M6" t="inlineStr">
-        <is>
-          <t>stationär</t>
-        </is>
-      </c>
+          <t>(Nyl.) Rehm</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
           <t>Lillrået, Lillrået, Ång</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>563091</v>
+        <v>563078</v>
       </c>
       <c r="R6" t="n">
-        <v>7062368</v>
+        <v>7062343</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1182,7 +1182,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>14:34</t>
+          <t>13:59</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1192,7 +1192,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>14:34</t>
+          <t>13:59</t>
         </is>
       </c>
       <c r="AD6" t="b">

--- a/artfynd/A 25051-2023 artfynd.xlsx
+++ b/artfynd/A 25051-2023 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>119834486</v>
+        <v>119833884</v>
       </c>
       <c r="B2" t="n">
-        <v>57431</v>
+        <v>79623</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,55 +687,41 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>103031</v>
+        <v>6458</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Lavskrika</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Perisoreus infaustus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="L2" t="inlineStr">
-        <is>
-          <t>i par</t>
-        </is>
-      </c>
-      <c r="M2" t="inlineStr">
-        <is>
-          <t>stationär</t>
-        </is>
-      </c>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
           <t>Lillrået, Lillrået, Ång</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>563091</v>
+        <v>563090</v>
       </c>
       <c r="R2" t="n">
-        <v>7062368</v>
+        <v>7062388</v>
       </c>
       <c r="S2" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -762,19 +748,9 @@
           <t>2024-09-18</t>
         </is>
       </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>14:34</t>
-        </is>
-      </c>
       <c r="AA2" t="inlineStr">
         <is>
           <t>2024-09-18</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>14:34</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -789,12 +765,12 @@
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
@@ -903,10 +879,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>119833884</v>
+        <v>119833907</v>
       </c>
       <c r="B4" t="n">
-        <v>79623</v>
+        <v>82321</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -919,21 +895,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6458</v>
+        <v>1312</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -943,13 +919,13 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>563090</v>
+        <v>563078</v>
       </c>
       <c r="R4" t="n">
-        <v>7062388</v>
+        <v>7062343</v>
       </c>
       <c r="S4" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -976,9 +952,19 @@
           <t>2024-09-18</t>
         </is>
       </c>
+      <c r="Z4" t="inlineStr">
+        <is>
+          <t>13:59</t>
+        </is>
+      </c>
       <c r="AA4" t="inlineStr">
         <is>
           <t>2024-09-18</t>
+        </is>
+      </c>
+      <c r="AB4" t="inlineStr">
+        <is>
+          <t>13:59</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -993,12 +979,12 @@
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
@@ -1107,10 +1093,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>119833907</v>
+        <v>119834486</v>
       </c>
       <c r="B6" t="n">
-        <v>82321</v>
+        <v>57431</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1119,38 +1105,52 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>1312</v>
+        <v>103031</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Lavskrika</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Perisoreus infaustus</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="L6" t="inlineStr">
+        <is>
+          <t>i par</t>
+        </is>
+      </c>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>stationär</t>
+        </is>
+      </c>
       <c r="P6" t="inlineStr">
         <is>
           <t>Lillrået, Lillrået, Ång</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>563078</v>
+        <v>563091</v>
       </c>
       <c r="R6" t="n">
-        <v>7062343</v>
+        <v>7062368</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1182,7 +1182,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>13:59</t>
+          <t>14:34</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1192,7 +1192,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>13:59</t>
+          <t>14:34</t>
         </is>
       </c>
       <c r="AD6" t="b">
